--- a/data/trans_orig/Q5418_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5418_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de lavarse la ropa en 2023</t>
+          <t>Población según si es capaz de lavarse la ropa en 2023 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99153</t>
+          <t>99602</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105162</t>
+          <t>105286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53760</t>
+          <t>53574</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62081</t>
+          <t>62211</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155936</t>
+          <t>155270</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>165903</t>
+          <t>165834</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81159</t>
+          <t>81605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90528</t>
+          <t>90864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38938</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44865</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122941</t>
+          <t>123023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134056</t>
+          <t>133940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24399</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82165</t>
+          <t>82241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93083</t>
+          <t>93160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36673</t>
+          <t>36650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45194</t>
+          <t>45164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122619</t>
+          <t>121728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136082</t>
+          <t>135687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35232</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>60818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>18595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34260</t>
+          <t>34042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54706</t>
+          <t>54319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172954</t>
+          <t>173804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193509</t>
+          <t>193519</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>282020</t>
+          <t>281090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>323592</t>
+          <t>322811</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>450880</t>
+          <t>450288</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>540249</t>
+          <t>538528</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>34015</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>31593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46978</t>
+          <t>47894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25160</t>
+          <t>25404</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>38776</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>31866</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>47108</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65507</t>
+          <t>66121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77426</t>
+          <t>77574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138149</t>
+          <t>137913</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155394</t>
+          <t>154743</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207882</t>
+          <t>207774</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228969</t>
+          <t>228045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32899</t>
+          <t>34461</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51957</t>
+          <t>52315</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35795</t>
+          <t>35126</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53960</t>
+          <t>54362</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27751</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43687</t>
+          <t>43343</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28714</t>
+          <t>28913</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45375</t>
+          <t>45416</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>231821</t>
+          <t>231322</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254233</t>
+          <t>254194</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>232711</t>
+          <t>231943</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>255582</t>
+          <t>255455</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>40661</t>
+          <t>40837</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62218</t>
+          <t>62588</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42892</t>
+          <t>44102</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>110827</t>
+          <t>109819</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86680</t>
+          <t>86300</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>161494</t>
+          <t>162834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38102</t>
+          <t>38742</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59604</t>
+          <t>59072</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48374</t>
+          <t>47445</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>117795</t>
+          <t>116366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>85951</t>
+          <t>88627</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>164221</t>
+          <t>165752</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>521523</t>
+          <t>520536</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>550837</t>
+          <t>549762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>793610</t>
+          <t>795583</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>926980</t>
+          <t>926940</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1333478</t>
+          <t>1332085</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1480577</t>
+          <t>1486016</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5418_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5418_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,57 +770,57 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>11621</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4483</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1696</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9902</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103044</t>
+          <t>115756</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99602</t>
+          <t>111960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105286</t>
+          <t>117910</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58838</t>
+          <t>67443</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53574</t>
+          <t>60280</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62211</t>
+          <t>70828</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>161882</t>
+          <t>183199</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155270</t>
+          <t>176563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>165834</t>
+          <t>187653</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>106996</t>
+          <t>119812</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106996</t>
+          <t>119812</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106996</t>
+          <t>119812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172317</t>
+          <t>194371</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172317</t>
+          <t>194371</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172317</t>
+          <t>194371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86969</t>
+          <t>96556</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81605</t>
+          <t>90897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90864</t>
+          <t>100455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>50212</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>45810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44714</t>
+          <t>52729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>129413</t>
+          <t>146768</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123023</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133940</t>
+          <t>151352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>26002</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88231</t>
+          <t>98381</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82241</t>
+          <t>92212</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93160</t>
+          <t>103084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41482</t>
+          <t>44911</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36650</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>49234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>129712</t>
+          <t>143292</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121728</t>
+          <t>135782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135687</t>
+          <t>149991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35108</t>
+          <t>36741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27954</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35509</t>
+          <t>38032</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>29984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60818</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19792</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>31722</t>
+          <t>33873</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54319</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>184520</t>
+          <t>202769</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173804</t>
+          <t>192129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193519</t>
+          <t>213280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>311298</t>
+          <t>114199</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>281090</t>
+          <t>108535</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>322811</t>
+          <t>119206</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>495818</t>
+          <t>316967</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>450288</t>
+          <t>304995</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>538528</t>
+          <t>329040</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>236356</t>
+          <t>257992</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>236356</t>
+          <t>257992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>236356</t>
+          <t>257992</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>563049</t>
+          <t>388872</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>563049</t>
+          <t>388872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>563049</t>
+          <t>388872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>22149</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34015</t>
+          <t>36485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>40708</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>32027</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>48889</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25404</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38776</t>
+          <t>41008</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>38564</t>
+          <t>42328</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47108</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>72242</t>
+          <t>79258</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66121</t>
+          <t>72422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77574</t>
+          <t>84650</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>146801</t>
+          <t>157813</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137913</t>
+          <t>148735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154743</t>
+          <t>167471</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>219043</t>
+          <t>237072</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207774</t>
+          <t>225672</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228045</t>
+          <t>247736</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>296281</t>
+          <t>320108</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296281</t>
+          <t>320108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296281</t>
+          <t>320108</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>46267</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52315</t>
+          <t>56530</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>47292</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35126</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54362</t>
+          <t>58151</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>35236</t>
+          <t>38328</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27336</t>
+          <t>29435</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43343</t>
+          <t>48123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>36370</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>31258</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45416</t>
+          <t>49610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>243484</t>
+          <t>260542</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>231322</t>
+          <t>248139</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254194</t>
+          <t>274071</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>244543</t>
+          <t>261614</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>231943</t>
+          <t>247254</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>255455</t>
+          <t>272121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>345137</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>345137</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>345137</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324284</t>
+          <t>348413</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324284</t>
+          <t>348413</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324284</t>
+          <t>348413</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>50421</t>
+          <t>52019</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>40837</t>
+          <t>41826</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62588</t>
+          <t>63825</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>84244</t>
+          <t>92125</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44102</t>
+          <t>78818</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>109819</t>
+          <t>105965</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>134666</t>
+          <t>144144</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86300</t>
+          <t>126135</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>162834</t>
+          <t>163440</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>48285</t>
+          <t>52318</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38742</t>
+          <t>41384</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59072</t>
+          <t>64807</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>89356</t>
+          <t>96931</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47445</t>
+          <t>85244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>116366</t>
+          <t>112119</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>137641</t>
+          <t>149249</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>88627</t>
+          <t>131536</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>165752</t>
+          <t>167391</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>536064</t>
+          <t>593794</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>520536</t>
+          <t>577037</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>549762</t>
+          <t>607512</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,67 +3722,67 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>844346</t>
+          <t>695120</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>795583</t>
+          <t>677696</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>926940</t>
+          <t>713520</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
+          <t>78,62%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>80,7%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1288913</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>1262250</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>1312488</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>81,46%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>79,77%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>82,95%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>78,16%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2147</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1380410</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>1332085</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>1486016</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>83,52%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>634770</t>
+          <t>698131</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>634770</t>
+          <t>698131</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>634770</t>
+          <t>698131</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>884175</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>884175</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>884175</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1652717</t>
+          <t>1582306</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1652717</t>
+          <t>1582306</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1652717</t>
+          <t>1582306</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
